--- a/astro-site/public/dl/plan-negocio-sushi-bar/plan-financiero-sushi-bar.xlsx
+++ b/astro-site/public/dl/plan-negocio-sushi-bar/plan-financiero-sushi-bar.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SIN IVA, por comensal: en sala, el menú del día de mediodía (14,90 € con IVA, un 30 % de la sala) y la cena o el fin de semana (28,60 € con IVA) dejan unos 22,26 € sin IVA; el pedido para llevar (un combinado de 24 piezas y un extra, 27,00 € con IVA) sale a 15,34 € por comensal equivalente y el de plataforma, con el precio un 15 % más alto, a 18,47 €. La media de los tres canales da 20,08 €; el caso se queda en 20,00 €. El precio con IVA está en la fila «PVP equivalente con IVA» de abajo</t>
+          <t>SIN IVA, por comensal: en sala, el menú del día de mediodía (14,90 € con IVA, un 30 % de la sala) y la cena o el fin de semana (28,60 € con IVA) dejan unos 22,26 € sin IVA; el pedido para llevar (de media 27,00 € con IVA: un combinado y algún extra) sale a 15,34 € por comensal equivalente y el de plataforma, con la carta un 15 % más cara y un pedido algo mayor, a 18,47 €. La media de los tres canales da 20,08 €; el caso se queda en 20,00 €. El precio con IVA está en la fila «PVP equivalente con IVA» de abajo</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="D14" s="29" t="inlineStr">
         <is>
-          <t>El congelador del anisakis tiene que llevar el pescado a -20 °C o menos en la totalidad del producto durante 24 horas (RD 1021/2022, art. 8.1) y registrar la temperatura; un congelador que sólo marca -18 °C no sirve para eso. El arcón, para el resto del congelado. Estimación del kit: pide la ficha técnica</t>
+          <t>El congelador del anisakis tiene que llevar el pescado a -20 °C o menos en la totalidad del producto durante al menos 24 horas, o a -35 °C o menos 15 horas (RD 1021/2022, art. 8.1), y registrar la temperatura; un congelador que sólo marca -18 °C no sirve para eso. El arcón, para el resto del congelado. Estimación del kit: pide la ficha técnica</t>
         </is>
       </c>
       <c r="E14" s="32" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D16" s="29" t="inlineStr">
         <is>
-          <t>Campana extractora con motor y filtros de grasa sobre la freidora, la plancha y la inducción (una de 1,5-2 m ronda los 815 € sin IVA)</t>
+          <t>Campana extractora con motor y filtros de grasa sobre la freidora, la plancha y la inducción (una de 1,5 a 2 m va de unos 543 a 813 € sin IVA)</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>Armario de pescado a 0-2 °C (el pescado fresco va a 4 °C o menos: RD 1021/2022, art. 4.1), armarios refrigerados de cocina, mesa refrigerada de trabajo para la barra y nevera de bebida y sake</t>
+          <t>Armario de pescado a 0-2 °C (el pescado fresco va entre 0 y 4 °C: RD 1021/2022, art. 4.1), armarios refrigerados de cocina, mesa refrigerada de trabajo para la barra y nevera de bebida y sake</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>Suelo de resultado neto a régimen para que el plan se sostenga. Un sushi bar bien llevado deja en torno a un 8-9 %. Estimación del kit</t>
+          <t>Suelo de resultado neto a régimen para que el plan se sostenga. Un sushi bar bien llevado deja en torno a un 8-10 %. Estimación del kit</t>
         </is>
       </c>
       <c r="G55" s="29" t="n"/>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="D44" s="48" t="inlineStr">
         <is>
-          <t>La comida preparada se refrigera, se mantiene a 63 °C o más o se sirve cuanto antes (RD 1086/2020, art. 30.2). El shari a temperatura ambiente sólo si tu APPCC lo justifica con evidencia científica y lo comunicas a sanidad: pH de cada tanda y tiempo máximo. Si no, refrigerado</t>
+          <t>La comida preparada se refrigera, se mantiene a 63 °C o más o se sirve cuanto antes (RD 1086/2020, art. 30.2). El shari a temperatura ambiente sólo si tu APPCC lo justifica con evidencia científica y lo demuestras a sanidad: pH de cada tanda y tiempo máximo. Si no, refrigerado</t>
         </is>
       </c>
       <c r="E44" s="29" t="n"/>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="O16" s="29" t="inlineStr">
         <is>
-          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en sala, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); la parte de la bebida que sale para llevar o a domicilio y declara la columna H de su línea (cerveza, sake, vino y refrescos con azúcares o edulcorantes añadidos), al general (art. 91.Uno.1.1.º a y b); la comida, también la que sale para llevar o a domicilio, al reducido (art. 91.Uno.2.2.º)</t>
+          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en sala, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); la parte de la bebida que sale para llevar o a domicilio y declara la columna H de su línea (cerveza, sake, vino y refrescos con azúcares o edulcorantes añadidos), al general (art. 91.Uno.1.1.º a y b); la comida, también la que sale para llevar o a domicilio, al reducido (art. 91.Uno.1.1.º y 2.2.º)</t>
         </is>
       </c>
     </row>
